--- a/Outputs/Scenarios/PtX_demand_HU_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HU_Electrification.xlsx
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>6.851511541074107e-05</v>
+        <v>6.851511541074105e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0002740604616429643</v>
+        <v>0.0002740604616429642</v>
       </c>
     </row>
     <row r="33">
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.006481122303662812</v>
+        <v>0.006481122303662813</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0.0001826352309920774</v>
       </c>
       <c r="K42" t="n">
-        <v>6.851511541074107e-05</v>
+        <v>6.851511541074105e-05</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_HU_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_HU_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002344042396197738</v>
       </c>
       <c r="K16" t="n">
-        <v>7.527055200336641e-05</v>
+        <v>0.0001724273250366932</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.254509200056107e-05</v>
+        <v>7.389742501572568e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5.018036800224428e-05</v>
+        <v>2.955897000629027e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7.527055200336641e-05</v>
+        <v>2.955897000629027e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001878519947735363</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0001379827705024073</v>
+        <v>0.0001354656125838919</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.001137068519571234</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0009864812636035936</v>
+        <v>0.0009684853274797894</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>3.377368313089167e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>1.254509200056107e-05</v>
+        <v>7.389742501572568e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.00347006938884947</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0004110906924644463</v>
+        <v>0.0008632904541753373</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>6.851511541074105e-05</v>
+        <v>3.699816232180018e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0002740604616429642</v>
+        <v>0.0001479926492872007</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0004110906924644463</v>
+        <v>0.0001479926492872007</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001826352309920774</v>
       </c>
       <c r="K42" t="n">
-        <v>6.851511541074105e-05</v>
+        <v>3.699816232180018e-05</v>
       </c>
     </row>
     <row r="43">
